--- a/data/trans_dic/P16A05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,37</t>
+          <t>1,81; 4,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,15</t>
+          <t>2,09; 5,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,79</t>
+          <t>1,47; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,04</t>
+          <t>3,21; 6,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,95</t>
+          <t>2,18; 4,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,09</t>
+          <t>5,36; 9,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,91</t>
+          <t>6,06; 10,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 8,72</t>
+          <t>5,92; 8,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,07</t>
+          <t>2,25; 4,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,81</t>
+          <t>4,14; 6,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,36</t>
+          <t>3,92; 6,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 6,94</t>
+          <t>4,91; 6,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,72</t>
+          <t>1,59; 3,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,26</t>
+          <t>2,0; 4,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,19</t>
+          <t>2,09; 4,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,97</t>
+          <t>1,29; 4,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,33</t>
+          <t>4,23; 7,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,89</t>
+          <t>6,53; 10,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,42</t>
+          <t>5,12; 8,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 11,84</t>
+          <t>8,81; 11,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,1</t>
+          <t>3,34; 5,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,59</t>
+          <t>4,54; 6,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,92</t>
+          <t>3,98; 5,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,22</t>
+          <t>4,07; 7,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,2</t>
+          <t>1,08; 3,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,19</t>
+          <t>1,96; 5,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,49</t>
+          <t>2,69; 5,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,76</t>
+          <t>3,52; 6,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,8</t>
+          <t>5,24; 8,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,04</t>
+          <t>4,32; 7,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,38</t>
+          <t>5,62; 9,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,12</t>
+          <t>2,95; 8,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,75</t>
+          <t>3,39; 5,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,87</t>
+          <t>3,58; 6,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,9</t>
+          <t>4,52; 7,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,84</t>
+          <t>3,59; 6,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,12</t>
+          <t>1,81; 3,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,44</t>
+          <t>2,45; 5,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,63</t>
+          <t>3,1; 5,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,62</t>
+          <t>3,81; 6,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,02</t>
+          <t>4,07; 6,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,73</t>
+          <t>5,55; 8,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,77</t>
+          <t>6,88; 10,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,07</t>
+          <t>6,17; 10,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,11</t>
+          <t>3,35; 5,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,69</t>
+          <t>4,52; 6,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,85</t>
+          <t>5,53; 7,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,94</t>
+          <t>5,7; 7,96</t>
         </is>
       </c>
     </row>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,21</t>
+          <t>2,07; 3,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,02</t>
+          <t>2,76; 4,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,24</t>
+          <t>2,87; 4,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,9</t>
+          <t>3,3; 4,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,14</t>
+          <t>4,6; 6,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,0</t>
+          <t>6,22; 8,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,55</t>
+          <t>6,78; 8,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 8,89</t>
+          <t>6,57; 8,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,54</t>
+          <t>3,5; 4,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,15</t>
+          <t>5,05; 6,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,77</t>
+          <t>5,26; 6,74</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12961; 30263</t>
+          <t>12558; 30591</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15413; 36080</t>
+          <t>14662; 36543</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9721; 25575</t>
+          <t>9935; 25793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19314; 38351</t>
+          <t>20359; 39108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14803; 34077</t>
+          <t>14998; 32954</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36449; 62959</t>
+          <t>37088; 63435</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39376; 66657</t>
+          <t>40757; 67411</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39189; 58927</t>
+          <t>39965; 59136</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30295; 56242</t>
+          <t>31017; 56736</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57541; 94855</t>
+          <t>57618; 90454</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54211; 85726</t>
+          <t>52800; 85534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63448; 90948</t>
+          <t>64368; 90416</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15400; 35814</t>
+          <t>15305; 35813</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20393; 43405</t>
+          <t>20335; 43430</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21921; 42829</t>
+          <t>21325; 43811</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16283; 47312</t>
+          <t>15407; 47910</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41547; 71020</t>
+          <t>40976; 71366</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64539; 101811</t>
+          <t>67181; 103981</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54324; 87775</t>
+          <t>53395; 88545</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84876; 113485</t>
+          <t>84446; 113521</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63676; 98357</t>
+          <t>64510; 100178</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92598; 134887</t>
+          <t>93008; 135726</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81271; 122348</t>
+          <t>82172; 123027</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90512; 155328</t>
+          <t>87583; 155634</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7360; 21731</t>
+          <t>7322; 21897</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14268; 39283</t>
+          <t>14804; 38831</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20057; 41699</t>
+          <t>20449; 42802</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23965; 47592</t>
+          <t>24748; 48213</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35200; 60212</t>
+          <t>35856; 60065</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34346; 62447</t>
+          <t>33560; 60855</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44138; 73638</t>
+          <t>44112; 73893</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27602; 75724</t>
+          <t>27488; 77418</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47399; 78301</t>
+          <t>46176; 75925</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54109; 89915</t>
+          <t>54878; 92666</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71283; 106591</t>
+          <t>69815; 108467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60745; 111943</t>
+          <t>58647; 113049</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18309; 38804</t>
+          <t>17057; 37129</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23874; 51498</t>
+          <t>23199; 49232</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29083; 52751</t>
+          <t>29050; 55196</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36608; 61311</t>
+          <t>35345; 60305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41934; 72873</t>
+          <t>42316; 71684</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57227; 91607</t>
+          <t>58215; 91993</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72822; 112441</t>
+          <t>71842; 110848</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68618; 109869</t>
+          <t>67381; 109994</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65859; 101218</t>
+          <t>66422; 101954</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91965; 133414</t>
+          <t>90215; 132786</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>108665; 155479</t>
+          <t>109481; 155511</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>114078; 160275</t>
+          <t>115011; 160734</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>68210; 105061</t>
+          <t>67807; 103312</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92671; 137543</t>
+          <t>94380; 141186</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100365; 144005</t>
+          <t>97572; 140507</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111138; 169391</t>
+          <t>114257; 169604</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155861; 207406</t>
+          <t>155481; 207452</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>225291; 283634</t>
+          <t>220617; 285627</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>238343; 303133</t>
+          <t>240366; 304472</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>231360; 325044</t>
+          <t>240418; 327373</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>235596; 301929</t>
+          <t>233080; 297133</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>329798; 410502</t>
+          <t>329289; 410329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>348475; 426976</t>
+          <t>350080; 429092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>376179; 481945</t>
+          <t>373970; 479385</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,41</t>
+          <t>1,89; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,21</t>
+          <t>2,15; 5,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,82</t>
+          <t>1,34; 3,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,16</t>
+          <t>3,05; 6,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,79</t>
+          <t>2,12; 4,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 9,16</t>
+          <t>5,28; 9,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,02</t>
+          <t>5,84; 9,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,76</t>
+          <t>5,79; 8,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,11</t>
+          <t>2,35; 4,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,49</t>
+          <t>4,14; 6,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,35</t>
+          <t>4,03; 6,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,9</t>
+          <t>4,81; 6,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,72</t>
+          <t>1,61; 3,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,27</t>
+          <t>2,0; 4,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,29</t>
+          <t>2,13; 4,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,02</t>
+          <t>2,19; 4,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,37</t>
+          <t>4,42; 7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,11</t>
+          <t>6,49; 9,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,49</t>
+          <t>5,14; 8,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 11,85</t>
+          <t>8,7; 11,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,19</t>
+          <t>3,3; 5,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,63</t>
+          <t>4,46; 6,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,96</t>
+          <t>3,95; 6,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,24</t>
+          <t>5,74; 7,62</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,23</t>
+          <t>1,14; 3,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,13</t>
+          <t>1,94; 5,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,64</t>
+          <t>2,66; 5,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,85</t>
+          <t>3,59; 6,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,78</t>
+          <t>5,21; 8,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,84</t>
+          <t>4,36; 8,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,41</t>
+          <t>5,55; 9,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,31</t>
+          <t>5,83; 8,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,57</t>
+          <t>3,43; 5,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,05</t>
+          <t>3,48; 5,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 7,02</t>
+          <t>4,61; 6,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,91</t>
+          <t>5,14; 7,32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,94</t>
+          <t>1,95; 4,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,2</t>
+          <t>2,51; 5,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,89</t>
+          <t>3,15; 5,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,51</t>
+          <t>3,68; 6,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,9</t>
+          <t>4,03; 6,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,76</t>
+          <t>5,63; 8,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 10,62</t>
+          <t>7,09; 10,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,08</t>
+          <t>7,11; 9,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,15</t>
+          <t>3,42; 5,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,65</t>
+          <t>4,48; 6,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,85</t>
+          <t>5,57; 7,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 7,96</t>
+          <t>5,85; 7,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,15</t>
+          <t>2,11; 3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,13</t>
+          <t>2,66; 4,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,14</t>
+          <t>2,94; 4,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,9</t>
+          <t>3,65; 5,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,14</t>
+          <t>4,53; 6,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,05</t>
+          <t>6,26; 8,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,95</t>
+          <t>7,74; 9,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,46</t>
+          <t>3,49; 4,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,89</t>
+          <t>4,75; 5,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,18</t>
+          <t>5,0; 6,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,74</t>
+          <t>5,89; 6,9</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>30859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>52209</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76876</t>
+          <t>83068</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12558; 30591</t>
+          <t>13108; 30428</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14662; 36543</t>
+          <t>15041; 35612</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9935; 25793</t>
+          <t>9069; 25117</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20359; 39108</t>
+          <t>21075; 42973</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14998; 32954</t>
+          <t>14627; 33757</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37088; 63435</t>
+          <t>36565; 64209</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40757; 67411</t>
+          <t>39306; 66226</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39965; 59136</t>
+          <t>42459; 62796</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31017; 56736</t>
+          <t>32417; 56774</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57618; 90454</t>
+          <t>57627; 93626</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52800; 85534</t>
+          <t>54278; 87502</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>64368; 90416</t>
+          <t>68453; 99187</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31660</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98922</t>
+          <t>108458</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>130582</t>
+          <t>141373</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15305; 35813</t>
+          <t>15478; 36049</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20335; 43430</t>
+          <t>20334; 41912</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21325; 43811</t>
+          <t>21746; 45798</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15407; 47910</t>
+          <t>22922; 45164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40976; 71366</t>
+          <t>42800; 73421</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67181; 103981</t>
+          <t>66753; 101559</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53395; 88545</t>
+          <t>53653; 87595</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84446; 113521</t>
+          <t>93215; 125613</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64510; 100178</t>
+          <t>63754; 99700</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93008; 135726</t>
+          <t>91300; 134944</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82172; 123027</t>
+          <t>81501; 124545</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87583; 155634</t>
+          <t>121635; 161613</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35069</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>59898</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89608</t>
+          <t>99217</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7322; 21897</t>
+          <t>7728; 21935</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14804; 38831</t>
+          <t>14666; 40582</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20449; 42802</t>
+          <t>20190; 43073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24748; 48213</t>
+          <t>28828; 53400</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35856; 60065</t>
+          <t>35612; 60752</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33560; 60855</t>
+          <t>33853; 64199</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44112; 73893</t>
+          <t>43553; 73781</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27488; 77418</t>
+          <t>47275; 72922</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46176; 75925</t>
+          <t>46751; 74971</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54878; 92666</t>
+          <t>53343; 91857</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69815; 108467</t>
+          <t>71244; 107807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58647; 113049</t>
+          <t>82962; 118150</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46870</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>93522</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>135534</t>
+          <t>140869</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17057; 37129</t>
+          <t>18327; 39144</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23199; 49232</t>
+          <t>23701; 50406</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29050; 55196</t>
+          <t>29578; 54862</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35345; 60305</t>
+          <t>36386; 62049</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42316; 71684</t>
+          <t>41849; 69717</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58215; 91993</t>
+          <t>59136; 91964</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71842; 110848</t>
+          <t>74002; 111479</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67381; 109994</t>
+          <t>79423; 109240</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66422; 101954</t>
+          <t>67733; 103533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90215; 132786</t>
+          <t>89319; 132670</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>109481; 155511</t>
+          <t>110283; 154958</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>115011; 160734</t>
+          <t>123356; 163332</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>290887</t>
+          <t>314087</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>432601</t>
+          <t>464527</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>67807; 103312</t>
+          <t>69233; 104896</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94380; 141186</t>
+          <t>91134; 138415</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97572; 140507</t>
+          <t>99860; 142104</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114257; 169604</t>
+          <t>128724; 176451</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155481; 207452</t>
+          <t>153029; 205573</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>220617; 285627</t>
+          <t>222140; 287276</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>240366; 304472</t>
+          <t>240175; 304450</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>240418; 327373</t>
+          <t>288698; 344031</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>233080; 297133</t>
+          <t>232017; 294823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>329289; 410329</t>
+          <t>330772; 412982</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>350080; 429092</t>
+          <t>347022; 426620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>373970; 479385</t>
+          <t>428107; 501395</t>
         </is>
       </c>
     </row>
